--- a/4.evidence/ELC/employees.xlsx
+++ b/4.evidence/ELC/employees.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -78,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,11 +88,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,7 +555,7 @@
           <t>代表取締役社長</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="6" t="n">
         <v>35886</v>
       </c>
       <c r="G2" s="5" t="n">
@@ -561,7 +563,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>yamamoto@sample-tp.co.jp</t>
+          <t>yamamoto@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -597,7 +599,7 @@
           <t>取締役CFO</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="6" t="n">
         <v>38443</v>
       </c>
       <c r="G3" s="5" t="n">
@@ -605,7 +607,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>watanabe@sample-tp.co.jp</t>
+          <t>watanabe@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -641,7 +643,7 @@
           <t>取締役COO</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="6" t="n">
         <v>36982</v>
       </c>
       <c r="G4" s="5" t="n">
@@ -649,7 +651,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>kobayashi@sample-tp.co.jp</t>
+          <t>kobayashi@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -685,7 +687,7 @@
           <t>経理部長</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="6" t="n">
         <v>37712</v>
       </c>
       <c r="G5" s="5" t="n">
@@ -693,7 +695,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>sato.i@sample-tp.co.jp</t>
+          <t>sato.i@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -733,7 +735,7 @@
           <t>経理部課長(財務会計)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="6" t="n">
         <v>39539</v>
       </c>
       <c r="G6" s="5" t="n">
@@ -741,7 +743,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>takahashi@sample-tp.co.jp</t>
+          <t>takahashi@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -777,7 +779,7 @@
           <t>経理部課長(管理会計)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="6" t="n">
         <v>40269</v>
       </c>
       <c r="G7" s="5" t="n">
@@ -785,7 +787,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>ito@sample-tp.co.jp</t>
+          <t>ito@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -821,7 +823,7 @@
           <t>経理部主任</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="6" t="n">
         <v>42095</v>
       </c>
       <c r="G8" s="5" t="n">
@@ -829,7 +831,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>nakamura@sample-tp.co.jp</t>
+          <t>nakamura@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -865,7 +867,7 @@
           <t>経理部担当</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="6" t="n">
         <v>43556</v>
       </c>
       <c r="G9" s="5" t="n">
@@ -873,7 +875,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>ogawa@sample-tp.co.jp</t>
+          <t>ogawa@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -909,7 +911,7 @@
           <t>経理部担当</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="6" t="n">
         <v>44287</v>
       </c>
       <c r="G10" s="5" t="n">
@@ -917,7 +919,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>ishii@sample-tp.co.jp</t>
+          <t>ishii@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -953,7 +955,7 @@
           <t>営業本部長</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="6" t="n">
         <v>36617</v>
       </c>
       <c r="G11" s="5" t="n">
@@ -961,7 +963,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>tanaka.t@sample-tp.co.jp</t>
+          <t>tanaka.t@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -997,7 +999,7 @@
           <t>営業部課長(自動車)</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="6" t="n">
         <v>38808</v>
       </c>
       <c r="G12" s="5" t="n">
@@ -1005,7 +1007,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>saito@sample-tp.co.jp</t>
+          <t>saito@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1041,7 +1043,7 @@
           <t>営業部課長(半導体)</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="6" t="n">
         <v>39539</v>
       </c>
       <c r="G13" s="5" t="n">
@@ -1049,7 +1051,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>fujita@sample-tp.co.jp</t>
+          <t>fujita@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1085,7 +1087,7 @@
           <t>営業部主任</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="6" t="n">
         <v>41730</v>
       </c>
       <c r="G14" s="5" t="n">
@@ -1093,7 +1095,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>matsumoto@sample-tp.co.jp</t>
+          <t>matsumoto@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1129,7 +1131,7 @@
           <t>営業部担当</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="6" t="n">
         <v>43191</v>
       </c>
       <c r="G15" s="5" t="n">
@@ -1137,7 +1139,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>inoue@sample-tp.co.jp</t>
+          <t>inoue@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1173,7 +1175,7 @@
           <t>購買部長</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="6" t="n">
         <v>37347</v>
       </c>
       <c r="G16" s="5" t="n">
@@ -1181,7 +1183,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>kimura@sample-tp.co.jp</t>
+          <t>kimura@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1217,7 +1219,7 @@
           <t>購買部課長</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="6" t="n">
         <v>39904</v>
       </c>
       <c r="G17" s="5" t="n">
@@ -1225,7 +1227,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>hayashi@sample-tp.co.jp</t>
+          <t>hayashi@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1265,7 +1267,7 @@
           <t>購買部主任</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="6" t="n">
         <v>41365</v>
       </c>
       <c r="G18" s="5" t="n">
@@ -1273,7 +1275,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>shimizu@sample-tp.co.jp</t>
+          <t>shimizu@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1309,7 +1311,7 @@
           <t>購買部担当</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="6" t="n">
         <v>42826</v>
       </c>
       <c r="G19" s="5" t="n">
@@ -1317,7 +1319,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>yamada@sample-tp.co.jp</t>
+          <t>yamada@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1353,7 +1355,7 @@
           <t>製造部長</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="6" t="n">
         <v>36982</v>
       </c>
       <c r="G20" s="5" t="n">
@@ -1361,7 +1363,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>mori@sample-tp.co.jp</t>
+          <t>mori@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1397,7 +1399,7 @@
           <t>製造課長</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="6" t="n">
         <v>39173</v>
       </c>
       <c r="G21" s="5" t="n">
@@ -1405,7 +1407,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>ikeda@sample-tp.co.jp</t>
+          <t>ikeda@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1441,7 +1443,7 @@
           <t>倉庫課長</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="6" t="n">
         <v>40269</v>
       </c>
       <c r="G22" s="5" t="n">
@@ -1449,7 +1451,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>hashimoto@sample-tp.co.jp</t>
+          <t>hashimoto@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1485,7 +1487,7 @@
           <t>情報システム部長</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="6" t="n">
         <v>38443</v>
       </c>
       <c r="G23" s="5" t="n">
@@ -1493,7 +1495,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>okada@sample-tp.co.jp</t>
+          <t>okada@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1533,7 +1535,7 @@
           <t>インフラチームリーダー</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="6" t="n">
         <v>40634</v>
       </c>
       <c r="G24" s="5" t="n">
@@ -1541,7 +1543,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>yoshida@sample-tp.co.jp</t>
+          <t>yoshida@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1581,7 +1583,7 @@
           <t>アプリチームリーダー</t>
         </is>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="6" t="n">
         <v>41000</v>
       </c>
       <c r="G25" s="5" t="n">
@@ -1589,7 +1591,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>kato@sample-tp.co.jp</t>
+          <t>kato@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1625,7 +1627,7 @@
           <t>ヘルプデスク</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="6" t="n">
         <v>43922</v>
       </c>
       <c r="G26" s="5" t="n">
@@ -1633,7 +1635,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>nishida@sample-tp.co.jp</t>
+          <t>nishida@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1669,7 +1671,7 @@
           <t>人事部長</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="6" t="n">
         <v>38078</v>
       </c>
       <c r="G27" s="5" t="n">
@@ -1677,7 +1679,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>kondo@sample-tp.co.jp</t>
+          <t>kondo@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1713,7 +1715,7 @@
           <t>人事部主任</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="6" t="n">
         <v>42461</v>
       </c>
       <c r="G28" s="5" t="n">
@@ -1721,7 +1723,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>nomura@sample-tp.co.jp</t>
+          <t>nomura@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1757,7 +1759,7 @@
           <t>総務部長</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="6" t="n">
         <v>38808</v>
       </c>
       <c r="G29" s="5" t="n">
@@ -1765,7 +1767,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>maeda@sample-tp.co.jp</t>
+          <t>maeda@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1801,7 +1803,7 @@
           <t>内部監査室長</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="6" t="n">
         <v>38443</v>
       </c>
       <c r="G30" s="5" t="n">
@@ -1809,7 +1811,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>hasegawa@sample-tp.co.jp</t>
+          <t>hasegawa@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1845,7 +1847,7 @@
           <t>内部監査担当</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="6" t="n">
         <v>42095</v>
       </c>
       <c r="G31" s="5" t="n">
@@ -1853,7 +1855,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>otsuka@sample-tp.co.jp</t>
+          <t>otsuka@sample-demoa.co.jp</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -1889,7 +1891,7 @@
           <t>営業部担当</t>
         </is>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="6" t="n">
         <v>43191</v>
       </c>
       <c r="G32" s="5" t="n">
@@ -1933,7 +1935,7 @@
           <t>購買部担当</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="6" t="n">
         <v>42826</v>
       </c>
       <c r="G33" s="5" t="n">
